--- a/Data/data documentation/download_bundles/v1/raw/Data documentation for council variables.xlsx
+++ b/Data/data documentation/download_bundles/v1/raw/Data documentation for council variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Github\philadelphia-council-districts-and-health\Data\data documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/tr842_drexel_edu/Documents/Github_repositories/philadelphia-council-districts-and-health/Data/data documentation/download_bundles/v1/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B5796-3466-4522-AE1C-06CF5B143E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{925B5796-3466-4522-AE1C-06CF5B143E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A197430A-B68F-2B4F-9B54-22B7DED44348}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7E76C4D9-7630-4340-BEBA-4E6127603C3B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" activeTab="1" xr2:uid="{7E76C4D9-7630-4340-BEBA-4E6127603C3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data documentation for council " sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="157">
   <si>
     <t>Map</t>
   </si>
@@ -363,9 +363,6 @@
     <t>Tree Canopy Coverage</t>
   </si>
   <si>
-    <t>Heat Vulnerabillity Index</t>
-  </si>
-  <si>
     <t xml:space="preserve">Variables Used: 
 #"B15003_001" = total pop over 25
 #"B15003_002" = No schooling
@@ -429,11 +426,6 @@
   </si>
   <si>
     <t>Variables Used:
-#B02001_001 Total pop
-#B03002_003 White Not hispanic or Latino</t>
-  </si>
-  <si>
-    <t>Variables Used:
 #B02001_001 Total pop,
 #B02001_003 Black</t>
   </si>
@@ -466,9 +458,6 @@
     <t>Variables Used:
 #B03001_001 Total pop,
 #B03002_012 Hispanic/Latino</t>
-  </si>
-  <si>
-    <t>Percentage of residents who are White, Non-hispanic</t>
   </si>
   <si>
     <t>Percentage of residents who are Hispanic</t>
@@ -607,6 +596,14 @@
   </si>
   <si>
     <t>Percentage of residents who are two or more races</t>
+  </si>
+  <si>
+    <t>Percentage of residents who are White, Non-Hispanic</t>
+  </si>
+  <si>
+    <t>Variables Used:
+#B02001_001 Total pop
+#B03002_003 White Not Hispanic or Latino</t>
   </si>
 </sst>
 </file>
@@ -1507,18 +1504,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CB8890-B7A9-3A40-979C-A48DC9A37105}">
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.296875" customWidth="1"/>
-    <col min="6" max="6" width="27.19921875" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.1640625" customWidth="1"/>
+    <col min="7" max="7" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1541,7 +1538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1564,7 +1561,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="265.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="289" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1587,7 +1584,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="358.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="388" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1610,7 +1607,7 @@
         <v>45726</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="204" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1633,7 +1630,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1656,7 +1653,7 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1679,7 +1676,7 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1702,7 +1699,7 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1722,7 +1719,7 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1745,7 +1742,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1768,7 +1765,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1791,7 +1788,7 @@
         <v>45726</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -1814,7 +1811,7 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="296.39999999999998" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="323" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -1837,7 +1834,7 @@
         <v>45726</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="221" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -1860,7 +1857,7 @@
         <v>45726</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="5" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" s="5" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1870,7 +1867,7 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1888,17 +1885,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B07AACCA-88DB-7C45-AECA-8998520502A5}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.19921875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.296875" style="2" customWidth="1"/>
-    <col min="4" max="5" width="11.19921875" style="2"/>
-    <col min="6" max="6" width="19.69921875" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="11.1640625" style="2"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -1921,7 +1918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>20</v>
       </c>
@@ -1944,17 +1941,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>65</v>
@@ -1966,15 +1963,15 @@
         <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>65</v>
@@ -1986,15 +1983,15 @@
         <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="62.4" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>65</v>
@@ -2006,18 +2003,18 @@
         <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="280.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="306" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>67</v>
@@ -2026,21 +2023,21 @@
         <v>66</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>67</v>
@@ -2049,21 +2046,21 @@
         <v>66</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="109.2" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="119" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>67</v>
@@ -2072,21 +2069,21 @@
         <v>66</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="109.2" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="119" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>67</v>
@@ -2095,21 +2092,21 @@
         <v>66</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="93.6" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -2118,18 +2115,18 @@
         <v>51</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>67</v>
@@ -2138,21 +2135,21 @@
         <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>67</v>
@@ -2161,13 +2158,13 @@
         <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="93.6" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>82</v>
       </c>
@@ -2184,21 +2181,21 @@
         <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="93.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>67</v>
@@ -2207,21 +2204,21 @@
         <v>66</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="93.6" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="102" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>67</v>
@@ -2230,21 +2227,21 @@
         <v>66</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>67</v>
@@ -2253,21 +2250,21 @@
         <v>66</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>67</v>
@@ -2276,21 +2273,21 @@
         <v>66</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>67</v>
@@ -2299,21 +2296,21 @@
         <v>66</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>67</v>
@@ -2322,21 +2319,21 @@
         <v>66</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>67</v>
@@ -2345,21 +2342,21 @@
         <v>66</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>67</v>
@@ -2368,21 +2365,21 @@
         <v>66</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>67</v>
@@ -2391,21 +2388,21 @@
         <v>66</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>67</v>
@@ -2414,18 +2411,18 @@
         <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="62.4" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>65</v>
@@ -2437,15 +2434,15 @@
         <v>47</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="62.4" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>65</v>
@@ -2457,18 +2454,18 @@
         <v>47</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>67</v>
@@ -2477,21 +2474,21 @@
         <v>66</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="109.2" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="119" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>36</v>
@@ -2500,15 +2497,15 @@
         <v>2019</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="109.2" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="119" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>7</v>
@@ -2523,21 +2520,21 @@
         <v>2018</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="78" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="85" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>67</v>
@@ -2546,10 +2543,10 @@
         <v>66</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
